--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -481,9 +481,17 @@
           <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>плита (возможно 0am325066ae)</t>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
@@ -498,1437 +506,1682 @@
           <t>Усиленная гидроплита + фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq200</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>фильтр (возможно 0AM325433E)</t>
+          <t>фильтр стандартный x1 -&gt; filtr-dsg7-dq200 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект (дубль)</t>
-        </is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>плита (возможно 0am325066ae)</t>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр мехатроника DQ200 DSG7, комплект (дубль)</t>
-        </is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq200</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>фильтр (возможно 0AM325433E)</t>
+          <t>фильтр стандартный x1 -&gt; filtr-dsg7-dq200 (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
-        </is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>плита</t>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-pylniki-sal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
-        </is>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>фильтр</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
-        </is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2 (возможно 122390AK-AF)</t>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
-        </is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>плита</t>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
-        </is>
+          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>фильтр (улучшенный)</t>
+          <t>сальник штока оригинал x2 -&gt; salnik-shtoka-orig (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2 (возможно 122390AKAF)</t>
+          <t>гидроплита (возможно 0am325066ae)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>плита</t>
+          <t>сальник(и) (уточните — сколько и оригинал/нет)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>0am325025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>фильтр</t>
+          <t>прокладка(и) (уточните какие именно)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
-        </is>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2</t>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + фильтр + 2 пыльника + 2 сальника DSG7 DQ200, полный комплект</t>
-        </is>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>сальник x2</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект (ПРОВЕРЬТЕ: нет пыльников в названии — так и задумано?)</t>
-        </is>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>плита</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект (ПРОВЕРЬТЕ: нет пыльников в названии — так и задумано?)</t>
-        </is>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>фильтр (улучшенный)</t>
+          <t>сальник штока x1 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект (ПРОВЕРЬТЕ: нет пыльников в названии — так и задумано?)</t>
-        </is>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>пыльник x1 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
-        </is>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>плита</t>
+          <t>крышка штока x1 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2</t>
+          <t>прокладка 1 (уточните)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DSG7 DQ200</t>
+          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>прокладка 2 (уточните, если больше одной)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7 (дубль)</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>плита</t>
+          <t>болт короткий (возможно 01X301127C)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7 (дубль)</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2</t>
+          <t>болт длинный (возможно WHT001922)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 оригинальных пыльника + 2 оригинальных сальника DQ200 DSG7 (дубль)</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>др. болты, если есть (уточните состав из 7 шт)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>гидроплита (возможно 0am325066ae)</t>
+          <t>гидроплита/прокладки (уточните состав)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>сальник(и) (уточните — сколько и оригинал/нет)</t>
+          <t>пыльник оригинал x2 (возможно 122390AKAF)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
+          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>прокладка(и) (уточните какие именно)</t>
+          <t>сальник оригинал x2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
-        </is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2</t>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
-        </is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>сальник x2</t>
+          <t>сальник штока оригинал x2 -&gt; salnik-shtoka-orig (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
-        </is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>2</v>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2 (возможно 0am325025q)</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
-        </is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0am325066AC</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>сальник x1</t>
+          <t>поршень усиленный x2 -&gt; 0am325066AC (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
-        </is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>пыльник x1</t>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
-        </is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x1 (возможно 0am325025q)</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
-        </is>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0am325091e</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>прокладка 1 (уточните)</t>
+          <t>шток длинный x1 -&gt; 0am325091e (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
-        </is>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>прокладка 2 (уточните, если больше одной)</t>
+          <t>втулка x1 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
-        </is>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0am325091f</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>болт короткий (возможно 01X301127C)</t>
+          <t>шток короткий x1 -&gt; 0am325091f (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
-        </is>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>болт длинный (возможно WHT001922)</t>
+          <t>втулка x1 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
-        </is>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0am325091e</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>др. болты, если есть (уточните состав из 7 шт)</t>
+          <t>шток длинный x2 -&gt; 0am325091e (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>гидроплита/прокладки (уточните состав)</t>
+          <t>втулка x2 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0am325091f</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2 (возможно 122390AKAF)</t>
+          <t>шток короткий x2 -&gt; 0am325091f (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>втулка x2 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
-        </is>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>02e305045</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2</t>
+          <t>корпус фильтра DSG6 x1 -&gt; 02e305045 (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
-        </is>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>02E305051C</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>фильтр DSG6 x1 -&gt; 02E305051C (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2</t>
+          <t>корпус фильтра x1 (возможно 0BH325183/korpus-filtra-0bh325159)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7 (дубль)</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2</t>
+          <t>фильтр x1 (не нашёл отдельного артикула в каталоге — уточните)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7 (дубль)</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>магнит x1 (возможно Ea888gen3, с маленькой буквы — другой товар!)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DQ200 DSG7 (дубль)</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2</t>
+          <t>корпус фильтра x1 (возможно EA888)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
-        </is>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0AM325219C</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>поршень усиленный x2 (возможно 0am325066AC)</t>
+          <t>крышка x1 -&gt; 0AM325219C (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
-        </is>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0AM325443D</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2</t>
+          <t>прокладка крышки x1 -&gt; 0AM325443D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
-        </is>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0AM325467J</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2</t>
+          <t>сепараторная пластина x1 -&gt; 0AM325467J (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки (дубль)</t>
-        </is>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>plastiny-solenoid-orig</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>поршень усиленный x2</t>
+          <t>пластины соленоидов x1 -&gt; plastiny-solenoid-orig (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки (дубль)</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2</t>
+          <t>прокладка(и) (уточните)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DQ200 DSG7: 2 усиленных поршня + 2 пыльника + 2 крышки (дубль)</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2</t>
+          <t>сальник оригинал (уточните кол-во)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>шток длинный x1 (возможно 0am325091e)</t>
+          <t>пыльник оригинал (уточните кол-во)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>втулка x1 (возможно 0am325025D)</t>
+          <t>подшипник x10 (уточните — продаётся ли этот же подшипник поштучно отдельным артикулом)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>шток короткий x1 (возможно 0am325091f)</t>
+          <t>подшипник x4 (уточните — продаётся ли поштучно, другая коробка — не DSG7)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
-        </is>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>0am325025P</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>втулка x1 (возможно 0am325025D)</t>
+          <t>клипса штока x2 -&gt; 0am325025P (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
-        </is>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>0am325477</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>шток длинный x2 (возможно 0am325091e)</t>
+          <t>планка соленоида x2 -&gt; 0am325477 (был только на WB, цену снизили, заводим на Ozon — подтверждено 2026-09-17)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
-        </is>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0am325025r</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>4</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>втулка x2 (возможно 0am325025D)</t>
+          <t>опорное кольцо толкателя усиленное (алюм.) x4 -&gt; 0am325025r (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
-        </is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2</v>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>шток короткий x2 (возможно 0am325091f)</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
-        </is>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>4</v>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>втулка x2 (возможно 0am325025D)</t>
+          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
-        </is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>4</v>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра x1 (возможно 02e305045)</t>
+          <t>толкатель вилки x4 -&gt; 0am325025l (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
-        </is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>4</v>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>фильтр x1 (возможно 02E305051C)</t>
+          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>4</v>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра x1 (возможно 0BH325183/korpus-filtra-0bh325159)</t>
+          <t>толкатель вилки x4 -&gt; 0am325025l (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
-        </is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>4</v>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>фильтр x1 (не нашёл отдельного артикула в каталоге — уточните)</t>
+          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
-        </is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0am325025r</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>4</v>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>магнит x1 (возможно Ea888gen3, с маленькой буквы — другой товар!)</t>
+          <t>опорное кольцо толкателя усиленное (алюм.) x4 -&gt; 0am325025r (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
-        </is>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра x1 (возможно EA888)</t>
+          <t>втулка (гильза) штока x2 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>крышка x1 (уточните — возможно 0AM325219C)</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>прокладка x1 (возможно 0AM325443D)</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>фильтр улучшенный x1 -&gt; 0AM325433E (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>сепараторная пластина x1 (возможно 0AM325467J)</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>пластины соленоидов (возможно 0am325477ae/plastiny-solenoid-orig)</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0AM325433E</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>фильтр улучшенный x1 -&gt; 0AM325433E (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>прокладка(и) (уточните)</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>сальник оригинал (уточните кол-во)</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>сальник штока оригинал x2 -&gt; salnik-shtoka-orig (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>пыльник оригинал (уточните кол-во)</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
-        </is>
-      </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>подшипник x10 (уточните — продаётся ли этот же подшипник поштучно отдельным артикулом)</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
-        <is>
-          <t>подшипник x4 (уточните — продаётся ли поштучно, другая коробка — не DSG7)</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>klipsy-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>клипса штока x2 (возможно 0am325025P)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>planka-solenoid-2sht</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>планка соленоида x2 (уточните — не нашёл отдельного 1-шт артикула)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>salnik-tolkatelya-alum</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя (алюм.) x4 (уточните — тот же артикул, что и 0AM325413A, или отдельный?)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>salniki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>сальник штока x2 (уточните — есть ли этот же сальник поштучно 1 шт)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>salniki-tolkatelya-4sht</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя x4 (возможно 0AM325413A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>толкатель вилки x4 (уточните артикул)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>tolkateli-4-salniki-4</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя x4 (возможно 0AM325413A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>толкатель вилки x4</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя x4 (возможно 0AM325413A)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>сальник алюм. усиленный x4</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>vtulki-shtokov-2sht</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>втулка (гильза) штока x2 (возможно 0am325025D)</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>

--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -691,120 +691,144 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>сальник штока оригинал x2 -&gt; salnik-shtoka-orig (подтверждено)</t>
+          <t>сальник штока оригинал x2 -&gt; 0сц (исправлено: старая ссылка salnik-shtoka-orig была мёртвым дублем без остатка, реальный артикул с остатком — 0сц)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
-        </is>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>гидроплита (возможно 0am325066ae)</t>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
-        </is>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>сальник(и) (уточните — сколько и оригинал/нет)</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0am325025</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки) 0AM325025</t>
-        </is>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>прокладка(и) (уточните какие именно)</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
+          <t>сальник штока x1 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
+          <t>пыльник x1 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: пыльники, сальники, крышки</t>
+          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -813,289 +837,345 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
+          <t>крышка штока x1 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>01X301127C</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>сальник штока x1 -&gt; 0am325066ad (подтверждено)</t>
+          <t>болт короткий x3 -&gt; 01X301127C (подтверждено пользователем: 3 коротких + 4 длинных = 7)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>пыльник x1 -&gt; 122390AK-AF (подтверждено)</t>
+          <t>болт длинный x4 -&gt; WHT001922 (подтверждено пользователем: 3 коротких + 4 длинных = 7)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>0am325025q</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
+          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
+        </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x1 -&gt; 0am325025q (подтверждено)</t>
+          <t>не требуется — 3 коротких + 4 длинных = 7, других болтов нет</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
-        </is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>прокладка 1 (уточните)</t>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ремкомплект прокладок мехатроника DSG7 DQ200 0AM325025M</t>
-        </is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>прокладка 2 (уточните, если больше одной)</t>
+          <t>сальник штока оригинал x2 -&gt; 0сц (исправлено: старая ссылка salnik-shtoka-orig была мёртвым дублем без остатка, реальный артикул с остатком — 0сц)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>remkomplekt-shtokov-orig</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
-        </is>
+          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>болт короткий (возможно 01X301127C)</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
-        </is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0am325066AC</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>болт длинный (возможно WHT001922)</t>
+          <t>поршень усиленный x2 -&gt; 0am325066AC (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0am325025f</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Комплект болтов мехатроника DSG7 DQ200, 7 шт</t>
-        </is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>122390AK-AF</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>др. болты, если есть (уточните состав из 7 шт)</t>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>porshni-usil-pylniki-kryshki</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
+          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0am325025q</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>гидроплита/прокладки (уточните состав)</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0am325091e</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2 (возможно 122390AKAF)</t>
+          <t>шток длинный x1 -&gt; 0am325091e (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0am325025u</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ремкомплект мехатроника DSG7 DQ200 + оригинальные пыльники и сальники VAG</t>
-        </is>
+          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0am325025D</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал x2</t>
+          <t>втулка x1 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
+          <t>шток короткий x1 -&gt; 0am325091f (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>0am325025z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>сальник штока оригинал x2 -&gt; salnik-shtoka-orig (подтверждено)</t>
+          <t>втулка x1 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Оригинальный ремкомплект 2 штоков VAG: пыльники, сальники, крышки DSG7 DQ200</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1103,24 +1183,24 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
+          <t>шток длинный x2 -&gt; 0am325091e (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0am325091e-set</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1128,24 +1208,24 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>поршень усиленный x2 -&gt; 0am325066AC (подтверждено)</t>
+          <t>втулка x2 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>122390AK-AF</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1153,24 +1233,24 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
+          <t>шток короткий x2 -&gt; 0am325091f (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki</t>
+          <t>0am325091f-set</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ремкомплект штоков DSG7 DQ200: 2 усиленных поршня + 2 пыльника + 2 крышки</t>
+          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1178,24 +1258,24 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
+          <t>втулка x2 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>02e305045</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1203,24 +1283,24 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>шток длинный x1 -&gt; 0am325091e (подтверждено)</t>
+          <t>корпус фильтра DSG6 x1 -&gt; 02e305045 (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0am325025u</t>
+          <t>02E 305 045</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный длинный шток 0AM325091E 101мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>02E305051C</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1228,24 +1308,24 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>втулка x1 -&gt; 0am325025D (подтверждено)</t>
+          <t>фильтр DSG6 x1 -&gt; 02E305051C (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1253,24 +1333,24 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>шток короткий x1 -&gt; 0am325091f (подтверждено)</t>
+          <t>корпус фильтра x1 -&gt; Dq500 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0am325025z</t>
+          <t>DQ500</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ремкомплект: Усиленный короткий шток 0AM325091F 99мм + втулка мехатроника DSG7 DQ200</t>
+          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1278,124 +1358,124 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>втулка x1 -&gt; 0am325025D (подтверждено)</t>
+          <t>фильтр x1 -&gt; filtr-dsg7-dq500 (подтверждено пользователем; ВНИМАНИЕ: товар пока только в new_products.xlsx, ещё не запущен на площадках)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>Ea888gen3</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>шток длинный x2 -&gt; 0am325091e (подтверждено)</t>
+          <t>магнит x1 -&gt; Ea888gen3 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0am325091e-set</t>
+          <t>EA888gen3</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 101мм 0AM325091E + 2 втулки DSG7 DQ200</t>
+          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>втулка x2 -&gt; 0am325025D (подтверждено)</t>
+          <t>корпус фильтра x1 -&gt; EA888 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>шток короткий x2 -&gt; 0am325091f (подтверждено)</t>
+          <t>крышка x1 -&gt; 0AM325219C (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0am325091f-set</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Комплект 2 усиленных штока 99мм 0AM325091F + 2 втулки DSG7 DQ200</t>
+          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>втулка x2 -&gt; 0am325025D (подтверждено)</t>
+          <t>прокладка крышки x1 -&gt; 0AM325443D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02e305045</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1403,652 +1483,684 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра DSG6 x1 -&gt; 02e305045 (подтверждено)</t>
+          <t>сепараторная пластина x1 -&gt; 0AM325467J (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>02E 305 045</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG6 DQ250 02E305045</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02E305051C</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>фильтр DSG6 x1 -&gt; 02E305051C (подтверждено)</t>
+          <t>пластины соленоидов x2 -&gt; 0am325477ae напрямую (подтверждено пользователем, без вложенности)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра x1 (возможно 0BH325183/korpus-filtra-0bh325159)</t>
+          <t>прокладка(и) (уточните)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DQ500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Корпус фильтра + фильтр мехатроника DSG7 DQ500, комплект</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>фильтр x1 (не нашёл отдельного артикула в каталоге — уточните)</t>
+          <t>сальник оригинал (уточните кол-во)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>магнит x1 (возможно Ea888gen3, с маленькой буквы — другой товар!)</t>
+          <t>пыльник оригинал (уточните кол-во)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EA888gen3</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Магнит + алюминиевый корпус фильтра EA888 Gen.3, комплект</t>
+          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>корпус фильтра x1 (возможно EA888)</t>
+          <t>подшипник x10 (уточните — продаётся ли этот же подшипник поштучно отдельным артикулом)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>0AM325219C</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
+          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
+        </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>крышка x1 -&gt; 0AM325219C (подтверждено)</t>
+          <t>подшипник x4 (уточните — продаётся ли поштучно, другая коробка — не DSG7)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Оригинальная крышка + усиленная прокладка мехатроника DSG7 DQ200</t>
+          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0am325025P</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>прокладка крышки x1 -&gt; 0AM325443D (подтверждено)</t>
+          <t>клипса штока x2 -&gt; 0am325025P (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>сепараторная пластина x1 -&gt; 0AM325467J (подтверждено)</t>
+          <t>планка соленоида x2 -&gt; 0am325477 (был только на WB, цену снизили, заводим на Ozon — подтверждено 2026-09-17)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG</t>
+          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>пластины соленоидов x1 -&gt; plastiny-solenoid-orig (подтверждено)</t>
+          <t>опорное кольцо толкателя усиленное (алюм.) x4 -&gt; 0am325025r (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
+          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0am325066ad</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2</v>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>прокладка(и) (уточните)</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
+          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>сальник оригинал (уточните кол-во)</t>
+          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Прокладки + сальники + пыльники мехатроника DSG7 DQ200, оригинал Германия</t>
-        </is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>4</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>пыльник оригинал (уточните кол-во)</t>
+          <t>толкатель вилки x4 -&gt; 0am325025l (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Комплект подшипников мехатроника DSG7 DQ200, 10 шт, оригинал NSK</t>
-        </is>
+          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0AM325413A</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>подшипник x10 (уточните — продаётся ли этот же подшипник поштучно отдельным артикулом)</t>
+          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Комплект подшипников вариатора JF011E (RE0F10A), 4 шт, оригинал NSK</t>
-        </is>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0am325025l</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>подшипник x4 (уточните — продаётся ли поштучно, другая коробка — не DSG7)</t>
+          <t>толкатель вилки x4 -&gt; 0am325025l (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Клипсы штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0am325025P</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>клипса штока x2 -&gt; 0am325025P (подтверждено)</t>
+          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>tolkateli-salniki-alum-komplekt</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Планки соленоидов мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>планка соленоида x2 -&gt; 0am325477 (был только на WB, цену снизили, заводим на Ozon — подтверждено 2026-09-17)</t>
+          <t>опорное кольцо толкателя усиленное (алюм.) x4 -&gt; 0am325025r (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Усиленные алюминиевые сальники толкателя с гальваническим покрытием, комплект 4 шт, DSG7 DQ200</t>
+          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>опорное кольцо толкателя усиленное (алюм.) x4 -&gt; 0am325025r (подтверждено пользователем)</t>
+          <t>втулка (гильза) штока x2 -&gt; 0am325025D (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Сальники штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Полный комплект сальников толкателей вилок мехатроника DSG7 DQ200, 4 шт</t>
+          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4</v>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>фильтр улучшенный x1 -&gt; 0AM325433E (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4</v>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>толкатель вилки x4 -&gt; 0am325025l (подтверждено)</t>
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Комплект 4 толкателей вилок + 4 сальника DSG7 DQ200, на весь мехатроник</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4</v>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>фильтр улучшенный x1 -&gt; 0AM325433E (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>122390AKAF</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>4</v>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>толкатель вилки x4 -&gt; 0am325025l (подтверждено)</t>
+        <v>2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>сальник толкателя (НЕ сальник штока!) x4 -&gt; 0AM325413A (подтверждено)</t>
+        <v>2</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>сальник штока оригинал x2 -&gt; 0сц (исправлено: старая ссылка salnik-shtoka-orig была мёртвым дублем без остатка, реальный артикул с остатком — 0сц)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Толкатели вилок + сальники + усиленные алюминиевые сальники DSG7 DQ200, комплект 4+4+4</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>4</v>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>опорное кольцо толкателя усиленное (алюм.) x4 -&gt; 0am325025r (подтверждено)</t>
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vtulki-shtokov-2sht</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Втулки (гильзы) штоков мехатроника DSG7 DQ200, комплект 2 шт</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>122390AK-AF</t>
         </is>
       </c>
       <c r="D67" t="n">
         <v>2</v>
       </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>втулка (гильза) штока x2 -&gt; 0am325025D (подтверждено)</t>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Усиленная плита + улучшенный фильтр мехатроника DSG7 DQ200, комплект</t>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200, оригинал VAG, комплект 2 шт</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0am325477ae</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>фильтр улучшенный x1 -&gt; 0AM325433E (подтверждено)</t>
+          <t>пластина соленоида x2 -&gt; 0am325477ae (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plastiny-solenoid-dq200-2sht</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Пластины на соленоиды мехатроника DSG7 DQ200, комплект 2 шт</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
+          <t>пластина x2 -&gt; plastina-solenoid-dq200 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2056,24 +2168,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>фильтр улучшенный x1 -&gt; 0AM325433E (подтверждено)</t>
+          <t>сепараторная пластина x1 -&gt; separatornaya-plastina-dq200 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>separatornaya-plastiny-solenoid-dq200</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Сепараторная пластина + пластины на соленоиды мехатроника DSG7 DQ200</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>122390AKAF</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2081,49 +2193,49 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>пыльник оригинал x2 -&gt; 122390AKAF (подтверждено)</t>
+          <t>пластины на соленоиды x2 -&gt; plastina-solenoid-dq200 (подтверждено пользователем)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Плита + фильтр + 2 пыльника + 2 сальника ориг VAG DSG7 DQ200, полный комплект</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>сальник штока оригинал x2 -&gt; salnik-shtoka-orig (подтверждено)</t>
+          <t>плита x1 -&gt; 0am325066ae (по аналогии с plita-filtr-pylniki-sal)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -2131,19 +2243,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>плита x1 -&gt; 0am325066ae (подтверждено)</t>
+          <t>фильтр стандартный x1 -&gt; filtr-dsg7-dq200</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Усиленная гидроплита + фильтр + 2 пыльника штоков DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2156,32 +2268,232 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
+          <t>пыльник x2 -&gt; 122390AK-AF</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Усиленная гидроплита + 2 пыльника + 2 сальника DSG7 DQ200, комплект без фильтра</t>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
+          <t>плита x1 -&gt; 0am325066ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq200</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>фильтр стандартный x1 -&gt; filtr-dsg7-dq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>plita-filtr-pylniki-orig</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных пыльника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>плита x1 -&gt; 0am325066ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>filtr-dsg7-dq200</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>фильтр стандартный x1 -&gt; filtr-dsg7-dq200</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>plita-filtr-salniki-orig</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Усиленная плита + фильтр + 2 оригинальных сальника VAG DSG7 DQ200, комплект</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>сальник штока оригинал x2 -&gt; 0сц</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>pylniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Оригинальные пыльники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>122390AKAF</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>пыльник оригинал x2 -&gt; 122390AKAF (по аналогии с klipsy-shtokov-2sht/vtulki-shtokov-2sht)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Оригинальные сальники штоков VAG, 2 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>сальник штока оригинал x2 -&gt; 0сц (по аналогии с salniki-shtokov-2sht)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Оригинальный сальник штока VAG, 1 шт, DSG7 DQ200</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0сц</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>сальник штока оригинал x1 -&gt; 0сц (та же деталь, что и 0сц, просто карточка на 1 шт, подтверждено пользователем)</t>
         </is>
       </c>
     </row>

--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2497,6 +2497,56 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>0am325025</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0am325066ae</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>гидроплита x1 -&gt; 0am325066ae (подтверждено пользователем)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>0am325025</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Ремкомплект мехатроника DSG7 DQ200 (гидроплита, сальники, прокладки)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>0am325025m</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>прокладки x1 -&gt; 0am325025m (подтверждено пользователем)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/kits.xlsx
+++ b/data/kits.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: 2 сальника, 2 пыльника, 2 крышки</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -787,11 +787,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>сальник штока x1 -&gt; 0am325066ad (подтверждено)</t>
+          <t>сальник штока x2 -&gt; 0am325066ad (подтверждено)</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: 2 сальника, 2 пыльника, 2 крышки</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -812,11 +812,11 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>пыльник x1 -&gt; 122390AK-AF (подтверждено)</t>
+          <t>пыльник x2 -&gt; 122390AK-AF (подтверждено)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ремкомплект штока мехатроника DSG7 DQ200: сальник, пыльник, крышка</t>
+          <t>Ремкомплект 2 штоков мехатроника DSG7 DQ200: 2 сальника, 2 пыльника, 2 крышки</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -837,11 +837,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>крышка штока x1 -&gt; 0am325025q (подтверждено)</t>
+          <t>крышка штока x2 -&gt; 0am325025q (подтверждено)</t>
         </is>
       </c>
     </row>
